--- a/src/reactormodels/IO/data/experimental_input_parameter.xlsx
+++ b/src/reactormodels/IO/data/experimental_input_parameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohammedfaran/Desktop/python_models/ReactorModels/src/reactormodels/IO/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64CC7A5-A979-0843-B2C8-B0C48EDDC78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D0003F-2419-3B40-8B3D-746A849273E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{8FC1EBE6-09F5-E544-BEAB-0C438D750464}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
   <si>
     <t>water</t>
   </si>
@@ -66,21 +66,12 @@
     <t>density</t>
   </si>
   <si>
-    <t>kg/m3</t>
-  </si>
-  <si>
     <t>viscosity</t>
   </si>
   <si>
-    <t>kg/(m-s)</t>
-  </si>
-  <si>
     <t>temperature</t>
   </si>
   <si>
-    <t>degrees C</t>
-  </si>
-  <si>
     <t>media</t>
   </si>
   <si>
@@ -93,9 +84,6 @@
     <t>mean_diameter</t>
   </si>
   <si>
-    <t>m</t>
-  </si>
-  <si>
     <t>bed_density</t>
   </si>
   <si>
@@ -129,18 +117,6 @@
     <t>sorbent_mass</t>
   </si>
   <si>
-    <t>breakthrough</t>
-  </si>
-  <si>
-    <t>parameters</t>
-  </si>
-  <si>
-    <t>flow_rate</t>
-  </si>
-  <si>
-    <t>superficial_velocity</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -240,13 +216,19 @@
     <t>boiling_point</t>
   </si>
   <si>
-    <t>m/s</t>
-  </si>
-  <si>
-    <t>m3/s</t>
-  </si>
-  <si>
     <t>experiment_id:</t>
+  </si>
+  <si>
+    <t>[M/L^3]</t>
+  </si>
+  <si>
+    <t>[M/(L-t)]</t>
+  </si>
+  <si>
+    <t>[L]</t>
+  </si>
+  <si>
+    <t>[T]</t>
   </si>
 </sst>
 </file>
@@ -281,13 +263,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -310,6 +285,13 @@
     <font>
       <sz val="9"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -396,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -404,43 +386,39 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -450,13 +428,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -793,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1156A5E6-1152-6E4D-AE94-8617611FAF4C}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -802,7 +787,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -810,11 +795,11 @@
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="22"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="20"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
@@ -846,44 +831,44 @@
         <v>997</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3">
         <v>8.8999999999999995E-4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3">
         <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="22"/>
+      <c r="A8" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>4</v>
@@ -891,29 +876,29 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3">
         <v>6.7500000000000001E-5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B11" s="3">
         <v>335</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -922,7 +907,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3">
         <v>0.31900000000000001</v>
@@ -933,69 +918,69 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B14" s="3">
         <v>600</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B15" s="3">
         <v>3.375E-5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="22"/>
+      <c r="A16" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>15</v>
+      <c r="A17" s="21" t="s">
+        <v>12</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>25</v>
+      <c r="A18" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="B18" s="6">
         <v>1.4989000000000001E-2</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>26</v>
+      <c r="A19" s="21" t="s">
+        <v>22</v>
       </c>
       <c r="B19" s="6">
         <v>3.1800000000000001E-3</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B20" s="6">
         <v>0.40799999999999997</v>
@@ -1004,64 +989,23 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="25"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="19">
-        <v>9.6333299999999996E-8</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="6">
-        <v>1.213E-2</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A23:C23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1092,91 +1036,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="J1" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="K1" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="L1" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="M1" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="N1" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="O1" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="P1" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="Q1" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="R1" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="S1" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="T1" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="U1" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="V1" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="W1" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="X1" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="Y1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="Z1" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="AA1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="T1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="X1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1206,8 +1150,8 @@
       <c r="AA2" s="3"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>62</v>
+      <c r="A3" s="22" t="s">
+        <v>54</v>
       </c>
       <c r="B3" s="7">
         <v>330.05</v>
@@ -1263,7 +1207,7 @@
       <c r="S3" s="7">
         <v>230.03800000000001</v>
       </c>
-      <c r="T3" s="9">
+      <c r="T3" s="8">
         <v>327.14</v>
       </c>
       <c r="U3" s="7">
@@ -1275,13 +1219,13 @@
       <c r="W3" s="7">
         <v>450.12</v>
       </c>
-      <c r="X3" s="10">
+      <c r="X3" s="9">
         <v>250.09</v>
       </c>
       <c r="Y3" s="7">
         <v>350.1</v>
       </c>
-      <c r="Z3" s="9">
+      <c r="Z3" s="8">
         <v>230.03800000000001</v>
       </c>
       <c r="AA3" s="3">
@@ -1289,104 +1233,104 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="11">
+      <c r="A4" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="10">
         <f>B3/B5</f>
         <v>188.6</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <f>C3/C5</f>
         <v>252.24456521739128</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <f>D3/D5</f>
         <v>129.72060606060606</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="10">
         <v>162</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <v>292</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <f>G3/G5</f>
         <v>212.90175438596492</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="10">
         <v>182</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="10">
         <v>217</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="10">
         <f>J3/J5</f>
         <v>111.12962962962962</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="10">
         <v>265</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="10">
         <f>L3/L5</f>
         <v>295.76881720430106</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="10">
         <f>M3/M5</f>
         <v>140.59257142857143</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="10">
         <f>N3/N5</f>
         <v>174.3262569832402</v>
       </c>
-      <c r="O4" s="11">
+      <c r="O4" s="10">
         <f>O3/O5</f>
         <v>212.388202247191</v>
       </c>
-      <c r="P4" s="11">
+      <c r="P4" s="10">
         <v>237</v>
       </c>
-      <c r="Q4" s="11">
+      <c r="Q4" s="10">
         <v>272</v>
       </c>
-      <c r="R4" s="11">
+      <c r="R4" s="10">
         <f>R3/R5</f>
         <v>158.11197604790422</v>
       </c>
-      <c r="S4" s="11">
+      <c r="S4" s="10">
         <f>S3/S5</f>
         <v>139.41696969696972</v>
       </c>
-      <c r="T4" s="9">
+      <c r="T4" s="8">
         <v>195</v>
       </c>
-      <c r="U4" s="11">
+      <c r="U4" s="10">
         <f>U3/U5</f>
         <v>254.85714285714289</v>
       </c>
-      <c r="V4" s="11">
+      <c r="V4" s="10">
         <f>V3/V5</f>
         <v>308.87134502923976</v>
       </c>
-      <c r="W4" s="11">
+      <c r="W4" s="10">
         <f>W3/W5</f>
         <v>242</v>
       </c>
-      <c r="X4" s="11">
+      <c r="X4" s="10">
         <f>X3/X5</f>
         <v>137.41208791208791</v>
       </c>
-      <c r="Y4" s="11">
+      <c r="Y4" s="10">
         <f>Y3/Y5</f>
         <v>191.31147540983608</v>
       </c>
-      <c r="Z4" s="9">
+      <c r="Z4" s="8">
         <v>134</v>
       </c>
       <c r="AA4" s="3"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="22" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="7">
@@ -1467,61 +1411,61 @@
       <c r="AA5" s="3"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="12">
+      <c r="A6" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="11">
         <v>5.5199999999999999E-2</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12">
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11">
         <v>2292.7640000000001</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12">
+      <c r="F6" s="11"/>
+      <c r="G6" s="11">
         <v>162.37165200000001</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>200.05239799999995</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <v>0</v>
       </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12">
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11">
         <v>0</v>
       </c>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
       <c r="AA6" s="3"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>65</v>
+      <c r="A7" s="22" t="s">
+        <v>57</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7">
         <v>6.37</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <v>0.23799999999999999</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <v>3.1099999999999999E-2</v>
       </c>
       <c r="G7" s="7">
@@ -1530,7 +1474,7 @@
       <c r="H7" s="7">
         <v>1.45</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <v>9.9500000000000005E-3</v>
       </c>
       <c r="J7" s="7">
@@ -1539,7 +1483,7 @@
       <c r="K7" s="7">
         <v>0.17100000000000001</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="11">
         <v>5.6499999999999996E-3</v>
       </c>
       <c r="M7" s="7"/>
@@ -1548,7 +1492,7 @@
       <c r="P7" s="7">
         <v>0.52500000000000002</v>
       </c>
-      <c r="Q7" s="12">
+      <c r="Q7" s="11">
         <v>7.7999999999999996E-3</v>
       </c>
       <c r="R7" s="7">
@@ -1565,8 +1509,8 @@
       <c r="AA7" s="3"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>66</v>
+      <c r="A8" s="22" t="s">
+        <v>58</v>
       </c>
       <c r="B8" s="7">
         <v>173</v>
@@ -1622,166 +1566,166 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="14"/>
+      <c r="A9" s="12"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A10" s="13"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
+      <c r="A10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A11" s="13"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
+      <c r="A11" s="12"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="14"/>
+      <c r="A12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
+      <c r="A13" s="12"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A14" s="13"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
+      <c r="A14" s="12"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
+      <c r="A15" s="12"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A16" s="13"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
+      <c r="A16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="13"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="14"/>
+      <c r="A17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="13"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
+      <c r="A18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="13"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
+      <c r="A19" s="12"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="13"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
+      <c r="A20" s="12"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="A21" s="12"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="13"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="A22" s="12"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="13"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="A23" s="12"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="A24" s="12"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="13"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
+      <c r="A25" s="12"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="14"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
+      <c r="A26" s="13"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/reactormodels/IO/data/experimental_input_parameter.xlsx
+++ b/src/reactormodels/IO/data/experimental_input_parameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohammedfaran/Desktop/python_models/ReactorModels/src/reactormodels/IO/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D0003F-2419-3B40-8B3D-746A849273E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681CBA1D-D258-3549-831A-B34AA4E845D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{8FC1EBE6-09F5-E544-BEAB-0C438D750464}"/>
   </bookViews>
@@ -81,9 +81,6 @@
     <t>value</t>
   </si>
   <si>
-    <t>mean_diameter</t>
-  </si>
-  <si>
     <t>bed_density</t>
   </si>
   <si>
@@ -229,6 +226,9 @@
   </si>
   <si>
     <t>[T]</t>
+  </si>
+  <si>
+    <t>particle_diameter</t>
   </si>
 </sst>
 </file>
@@ -419,15 +419,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -442,6 +433,15 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -787,7 +787,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -795,11 +795,11 @@
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="20"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="26"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
@@ -831,7 +831,7 @@
         <v>997</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -842,7 +842,7 @@
         <v>8.8999999999999995E-4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -853,15 +853,15 @@
         <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
@@ -879,10 +879,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="3">
-        <v>6.7500000000000001E-5</v>
+        <v>335</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -890,30 +890,30 @@
         <v>15</v>
       </c>
       <c r="B11" s="3">
-        <v>335</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>60</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="3">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="3">
-        <v>0.31900000000000001</v>
+        <v>600</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -921,32 +921,32 @@
         <v>18</v>
       </c>
       <c r="B14" s="3">
-        <v>600</v>
+        <v>3.375E-5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="3">
+        <v>6.7500000000000001E-5</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="3">
-        <v>3.375E-5</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="20"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="26"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -957,30 +957,30 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="21" t="s">
-        <v>21</v>
+      <c r="A18" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="B18" s="6">
         <v>1.4989000000000001E-2</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="21" t="s">
-        <v>22</v>
+      <c r="A19" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="B19" s="6">
         <v>3.1800000000000001E-3</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="6">
         <v>0.40799999999999997</v>
@@ -989,14 +989,14 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1036,91 +1036,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="C1" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="D1" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="E1" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="F1" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="G1" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="H1" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="I1" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="J1" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="K1" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="L1" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="M1" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="N1" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="O1" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="25" t="s">
+      <c r="P1" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="Q1" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="Q1" s="25" t="s">
+      <c r="R1" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="R1" s="25" t="s">
+      <c r="S1" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="S1" s="25" t="s">
+      <c r="T1" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="T1" s="25" t="s">
+      <c r="U1" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="U1" s="25" t="s">
+      <c r="V1" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="V1" s="25" t="s">
+      <c r="W1" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="W1" s="25" t="s">
+      <c r="X1" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="X1" s="25" t="s">
+      <c r="Y1" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="Y1" s="25" t="s">
+      <c r="Z1" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="Z1" s="26" t="s">
+      <c r="AA1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AA1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
-        <v>53</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1150,8 +1150,8 @@
       <c r="AA2" s="3"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
-        <v>54</v>
+      <c r="A3" s="19" t="s">
+        <v>53</v>
       </c>
       <c r="B3" s="7">
         <v>330.05</v>
@@ -1233,8 +1233,8 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="23" t="s">
-        <v>55</v>
+      <c r="A4" s="20" t="s">
+        <v>54</v>
       </c>
       <c r="B4" s="10">
         <f>B3/B5</f>
@@ -1330,7 +1330,7 @@
       <c r="AA4" s="3"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="19" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="7">
@@ -1411,8 +1411,8 @@
       <c r="AA5" s="3"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="24" t="s">
-        <v>56</v>
+      <c r="A6" s="21" t="s">
+        <v>55</v>
       </c>
       <c r="B6" s="11">
         <v>5.5199999999999999E-2</v>
@@ -1454,8 +1454,8 @@
       <c r="AA6" s="3"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A7" s="22" t="s">
-        <v>57</v>
+      <c r="A7" s="19" t="s">
+        <v>56</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1509,8 +1509,8 @@
       <c r="AA7" s="3"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
-        <v>58</v>
+      <c r="A8" s="19" t="s">
+        <v>57</v>
       </c>
       <c r="B8" s="7">
         <v>173</v>
